--- a/assets/BTS_SIO_Annexe_6_Epreuve E5 - Tableau de synthese_2026.xlsx
+++ b/assets/BTS_SIO_Annexe_6_Epreuve E5 - Tableau de synthese_2026.xlsx
@@ -1262,7 +1262,7 @@
     <row r="5" ht="39.95" customHeight="1" thickBot="1">
       <c r="A5" s="56" t="inlineStr">
         <is>
-          <t>Adresse URL du portfolio :</t>
+          <t>Adresse URL du portfolio : https://sahed-portfolio.pages.dev/</t>
         </is>
       </c>
       <c r="B5" s="57" t="n"/>
